--- a/output/pdf_financials_xlsx/MRKI.P.xlsx
+++ b/output/pdf_financials_xlsx/MRKI.P.xlsx
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.054242</v>
+        <v>-0.054242</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.102305</v>
+        <v>-0.102305</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.04034</v>
+        <v>-0.04034</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.039947</v>
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="17">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.054242</v>
+        <v>-0.054242</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.102305</v>
+        <v>-0.102305</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.04034</v>
+        <v>-0.04034</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.039947</v>
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="21">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.054242</v>
+        <v>-0.054242</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.102305</v>
+        <v>-0.102305</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.04034</v>
+        <v>-0.04034</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.039947</v>
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="24">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.008963</v>
+        <v>-2.008963</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2.0461</v>
+        <v>-2.0461</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2.017</v>
+        <v>-2.017</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1.99735</v>
+        <v>-1.99735</v>
       </c>
     </row>
     <row r="27">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.054242</v>
+        <v>-0.054242</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.102305</v>
+        <v>-0.102305</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.04034</v>
+        <v>-0.04034</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.039947</v>
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.054242</v>
+        <v>-0.054242</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.102305</v>
+        <v>-0.102305</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.04034</v>
+        <v>-0.04034</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.039947</v>
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="30">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.04034</v>
+        <v>-0.04034</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.039947</v>
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="30">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.054242</v>
+        <v>-0.054242</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.102305</v>
+        <v>-0.102305</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.04034</v>
+        <v>-0.04034</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MRKI.P.xlsx
+++ b/output/pdf_financials_xlsx/MRKI.P.xlsx
@@ -1076,25 +1076,17 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.060127</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.184759</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0.121678</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.08115</v>
       </c>
     </row>
     <row r="35">
@@ -1103,25 +1095,17 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1130,25 +1114,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.060127</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.184759</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.121678</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.08115</v>
       </c>
     </row>
     <row r="37">
@@ -1157,25 +1133,17 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1184,25 +1152,17 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1211,25 +1171,17 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1238,25 +1190,17 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1265,25 +1209,17 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1292,25 +1228,17 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1319,25 +1247,17 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1346,25 +1266,17 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1373,25 +1285,17 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1400,25 +1304,17 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1427,25 +1323,17 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1454,25 +1342,17 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1508,25 +1388,17 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1535,25 +1407,17 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1562,25 +1426,17 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1589,25 +1445,17 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1616,25 +1464,17 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1670,25 +1510,17 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1697,25 +1529,17 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1724,25 +1548,17 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1751,25 +1567,17 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1778,25 +1586,17 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1805,25 +1605,17 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1859,25 +1651,17 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>0.090877</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0.184759</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.121678</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.08115</v>
       </c>
     </row>
     <row r="64">
@@ -1886,25 +1670,17 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1913,25 +1689,17 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1940,25 +1708,17 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1967,25 +1727,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1994,25 +1746,17 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.026559</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.039924</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.017183</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.016602</v>
       </c>
     </row>
     <row r="69">
@@ -2021,25 +1765,17 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2048,25 +1784,17 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2075,25 +1803,17 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2102,25 +1822,17 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2129,25 +1841,17 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2156,25 +1860,17 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2183,25 +1879,17 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2237,25 +1925,17 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2264,25 +1944,17 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2291,25 +1963,17 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2345,25 +2009,17 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2372,25 +2028,17 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2399,25 +2047,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2426,25 +2066,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2453,25 +2085,17 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2507,25 +2131,17 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.026559</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.039924</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.017183</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.016602</v>
       </c>
     </row>
     <row r="88">
@@ -2534,25 +2150,17 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.26121</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.26121</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.26121</v>
       </c>
     </row>
     <row r="89">
@@ -2561,25 +2169,17 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2588,25 +2188,17 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-0.054242</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>-0.156547</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>-0.196887</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-0.236834</v>
       </c>
     </row>
     <row r="91">
@@ -2615,25 +2207,17 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2642,25 +2226,17 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0.040172</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0.040172</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.040172</v>
       </c>
     </row>
     <row r="93">
@@ -2669,25 +2245,17 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2696,25 +2264,17 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.064318</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.144835</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.104495</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.06454799999999999</v>
       </c>
     </row>
     <row r="95">
@@ -2723,25 +2283,17 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2750,25 +2302,17 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.064318</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.144835</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.104495</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.06454799999999999</v>
       </c>
     </row>
     <row r="97">
@@ -2777,25 +2321,17 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.70774783498575</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.7839130976028231</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.8587830174723451</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.7954158964879852</v>
       </c>
     </row>
     <row r="98">
@@ -3543,7 +3079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3597,315 +3133,299 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0.060127</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.184759</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.04034</v>
+        <v>0.121678</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-0.039947</v>
+        <v>0.08115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Total assets $</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0.090877</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.013365</v>
+        <v>0.184759</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.022741</v>
+        <v>0.121678</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-0.000581</v>
+        <v>0.08115</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Accounts payable and accrued liabilities $</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.026559</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.036578</v>
+        <v>0.039924</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.063081</v>
+        <v>0.017183</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-0.040528</v>
+        <v>0.016602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Decrease in cash during the year</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Capital stock (note 5)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.26121</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.063081</v>
+        <v>0.26121</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.040528</v>
+        <v>0.26121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Share-based payments reserve</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.040172</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.184759</v>
+        <v>0.040172</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.121678</v>
+        <v>0.040172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.054242</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.156547</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.121678</v>
+        <v>-0.196887</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.08115</v>
+        <v>-0.236834</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Shareholders’ equity</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>For the Years Ended October 31, 2023 and October</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shareholders’ equity total</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.064318</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.144835</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.104495</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.06454799999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Net Loss $</t>
+          <t>Total liabilities and shareholders’ equity $</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.054242</v>
+        <v>0.090877</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.102305</v>
+        <v>0.184759</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.04034</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.121678</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.08115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Items not requiring the use of cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="5" t="n">
-        <v>0.01856</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.021612</v>
+        <v>0.03075</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3926,32 +3446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0.03075</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.04034</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="12">
@@ -3962,34 +3484,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Issuance of capital stock</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.1</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013365</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.022741</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.000581</v>
       </c>
     </row>
     <row r="13">
@@ -4000,17 +3520,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4019,17 +3539,13 @@
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-0.05879</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.036578</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-0.063081</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>-0.040528</v>
       </c>
     </row>
     <row r="14">
@@ -4040,30 +3556,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financing total</t>
+          <t>Decrease in cash during the year</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.16121</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-0.063081</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-0.040528</v>
       </c>
     </row>
     <row r="15">
@@ -4074,30 +3590,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Increase in cash during the year</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>0.124632</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.063081</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.184759</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.121678</v>
       </c>
     </row>
     <row r="16">
@@ -4108,17 +3628,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4126,16 +3646,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>0.060127</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.184759</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.121678</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.08115</v>
       </c>
     </row>
     <row r="17">
@@ -4144,31 +3664,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Financing</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>For the Years Ended October 31, 2023 and October</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.184759</v>
+        <v>0.002022</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.121678</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -4182,23 +3694,29 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>For the Year Ended October 31, 2022 and the Period from Date of Incorporation (August</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Net Loss $</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
-        <v>0.002021</v>
+        <v>-0.054242</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.102305</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.04034</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -4212,18 +3730,26 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Items not requiring the use of cash</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>to October</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
-        <v>0.002021</v>
+        <v>0.01856</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.021612</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4244,7 +3770,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>capital</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4253,8 +3779,10 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" s="5" t="n">
-        <v>-0.03075</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.03075</v>
@@ -4278,24 +3806,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Issuance of capital stock</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>IssuanceOfCapitalStock</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.026559</v>
+        <v>0.1</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.013365</v>
+        <v>0.22</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4316,24 +3844,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Net cash used in operating</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>-0.039873</v>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.036578</v>
+        <v>-0.05879</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -4359,15 +3889,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Increase in cash during the period</t>
+          <t>Financing total</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
-        <v>0.060127</v>
+        <v>0.1</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.124632</v>
+        <v>0.16121</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -4388,31 +3918,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents,</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of period</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Increase in cash during the year</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.060127</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.124632</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.063081</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -4428,29 +3952,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period $</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>0.060127</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="G25" s="5" t="n">
         <v>0.184759</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4461,242 +3985,238 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Accounting and audit fees</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="5" t="n">
+        <v>0.184759</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.019792</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>0.017572</v>
+        <v>0.121678</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.010267</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>0.009466</v>
+          <t>For the Year Ended October 31, 2022 and the Period from Date of Incorporation (August</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Transfer agent, listing and other operating</t>
+          <t>to October</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.010281</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>0.012909</v>
+      <c r="E28" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>capital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>-0.04034</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>-0.039947</v>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" s="5" t="n">
+        <v>-0.03075</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.03075</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Accounts payable and accrued</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (Note 7) $</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>2e-08</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.026559</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.013365</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Net cash used in operating</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares total</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>-0.039873</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>2</v>
+        <v>-0.036578</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>For the Years Ended October 31, 2023 and October</t>
+          <t>Increase in cash during the period</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" s="5" t="n">
+        <v>0.060127</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.124632</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4707,22 +4227,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash and cash equivalents,</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
+          <t>Cash and cash equivalents, beginning of period</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4731,10 +4251,12 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.045977</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.030059</v>
+        <v>0.060127</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4745,25 +4267,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash and cash equivalents, end of</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of period $</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
-        <v>0.01856</v>
+        <v>0.060127</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.021612</v>
+        <v>0.184759</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4789,27 +4315,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0.013379</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>0.034716</v>
+          <t>Accounting and audit fees</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.010281</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019792</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.017572</v>
       </c>
     </row>
     <row r="36">
@@ -4825,27 +4349,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>-0.054242</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>-0.102305</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.04034</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010267</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.009466</v>
       </c>
     </row>
     <row r="37">
@@ -4861,27 +4387,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>2.7e-08</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>5e-08</v>
+          <t>Transfer agent, listing and other operating</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010281</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.012909</v>
       </c>
     </row>
     <row r="38">
@@ -4890,28 +4414,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>For the Year Ended October 31, 2022 and the Period from Date of Incorporation (August</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.04034</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>-0.039947</v>
       </c>
     </row>
     <row r="39">
@@ -4920,28 +4452,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>to October</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per share (Note 7) $</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>2e-08</v>
       </c>
     </row>
     <row r="40">
@@ -4952,31 +4492,335 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares total</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>For the Years Ended October 31, 2023 and October</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0.045977</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.030059</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.021612</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>General and administration</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.013379</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0.034716</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.010281</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>-0.054242</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>-0.102305</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.04034</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>2.7e-08</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>For the Year Ended October 31, 2022 and the Period from Date of Incorporation (August</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>to October</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Professional fees</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E49" s="5" t="n">
         <v>0.022203</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F49" s="5" t="n">
         <v>0.045977</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
